--- a/membrane_model/membrane_module_data_template.xlsx
+++ b/membrane_model/membrane_module_data_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t xml:space="preserve">Property</t>
   </si>
@@ -55,49 +55,52 @@
     <t xml:space="preserve">Mass flow of feed</t>
   </si>
   <si>
+    <t xml:space="preserve">Membrane thickness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">permeate_pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressure on permeate side of membrane.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">initial temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature of feed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial Pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressure of feed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coefficient to calculate sherwood number. Property of membrane material.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Membrane Length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">permeate_pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pressure on permeate side of membrane.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">initial temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature of feed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initial Pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pressure of feed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coefficient to calculate sherwood number. Property of membrane material.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a4</t>
   </si>
 </sst>
 </file>
@@ -308,7 +311,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.36"/>
@@ -364,7 +367,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>10</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -375,7 +378,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -389,7 +392,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>90000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -403,7 +406,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>353</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -474,6 +477,17 @@
       </c>
       <c r="D12" s="1" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
